--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0098.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0098.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Hợp Nhất Chỉ Định</t>
+          <t>Hợp Nhất Có Mục Tiêu</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Tiêu Chuẩn Merge</t>
+          <t>Hợp nhất tiêu chuẩn</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Hợp Nhất Chỉ Định</t>
+          <t>Hợp Nhất Có Mục Tiêu</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Tiêu Chuẩn Merge</t>
+          <t>Hợp nhất tiêu chuẩn</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Đã Áp Dụng Cài Đặt Đề Xuất</t>
+          <t>Đã áp dụng Cài Đặt Đề Xuất</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Motorbike Accessory</t>
+          <t>Phụ kiện Xe máy</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Chassis Mod</t>
+          <t>Nâng Cấp Khung Xe</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Default</t>
+          <t>Mặc định</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Bạn không thể chuyển Chassis khi đang lái</t>
+          <t>Bạn không thể thay đổi Khung gầm khi đang lái</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Đạt 10.000 điểm trong Stability Accords ở "Doubled Pawns Matrix: Pilot"</t>
+          <t>Đạt 10.000 điểm trong Hiệp Ước Ổn Định ở "Ma Trận Tốt Đôi: Phi Công"</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Đạt Vibe Level 6 trong "Where Stars Cascade Down"</t>
+          <t>Đạt Cấp Cảm Xúc 6 trong "Nơi Sao Rơi".</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Đạt Vibe Level 9 trong "Where Stars Cascade Down"</t>
+          <t>Đạt Cấp Cảm Xúc 9 trong "Nơi Sao Rơi".</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Đạt Rank Level 15 trong "Peaks of Prestige: Rekindled Duel"</t>
+          <t>Đạt Cấp Bậc 15 trong "Đỉnh Danh Vọng: Duel Tái Sinh"</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Thám Hiểm "The Song of Ice and Steel"</t>
+          <t>Hoàn thành Nhiệm Vụ Thám Hiểm "Khúc Ca Băng Giá và Thép"</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Mở khóa Đường Đua Băng Giá cho xe máy thám hiểm</t>
+          <t>Mở khóa Đường Đua Băng Giá cho xe thám hiểm</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Hoàn thành Chuyện Sau Cùng "Tất Cả Ánh Nắng Chạm Đến"</t>
+          <t>Hoàn thành Câu Chuyện Sau "Ánh Nắng Chạm Đến Mọi Thứ"</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 1.000 Điểm Hoạt Động</t>
+          <t>Đạt tổng cộng 1.000 Điểm Hoạt Động</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Untuned</t>
+          <t>Chưa Điều Chỉnh</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Sucessfully Upgraded</t>
+          <t>Nâng Cấp Thành Công</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Mở khóa tính năng Sự Kiện</t>
+          <t>Mở khóa chức năng Sự Kiện</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Đến Vùng Đất Băng Giá</t>
+          <t>Vào Vùng Đất Băng Giá</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Polar Expedition</t>
+          <t>Thám Hiểm Vùng Cực</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Frozen Exploration</t>
+          <t>Thám Hiểm Băng Giá</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Long Way Home</t>
+          <t>Con Đường Về Nhà Xa Xôi</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Dùng Projector: Glommoth để phá vỡ một số khối băng nhất định</t>
+          <t>Dùng Máy Chiếu: Glommoth để đập vỡ các khối băng nhất định</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách Điểm Kho Báu cụ thể</t>
+          <t>Hoàn thành các thử thách Điểm Kho Báu đặc biệt</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Đi vào trận tuyết rơi cùng Aemeath</t>
+          <t>Đi vào màn tuyết rơi cùng Aemeath.</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Bắt kịp Sigillum tại Địa Điểm Nghỉ Ngơi Exostrider</t>
+          <t>Đuổi theo Sigillum tại Bãi Nghỉ Exostrider</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách Hướng Dẫn Soliskin cụ thể</t>
+          <t>Hoàn thành các thử thách Hướng Dẫn Soliskin đặc biệt</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Hoàn thành một trận chiến trong Khu Vực Bão Hư Không nhất định</t>
+          <t>Hoàn thành một trận chiến trong Khu Bão Hư Không nhất định</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách Đua Xe Máy cụ thể</t>
+          <t>Hoàn thành các thử thách Đua Xe Máy đặc biệt</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Khám Phá "Bản Hùng Ca Của Băng Và Thép"</t>
+          <t>Hoàn thành Nhiệm Vụ Thám Hiểm "Khúc Ca Băng Giá và Thép"</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Khám Phá "Hy Vọng Không Băng Giá"</t>
+          <t>Hoàn thành Nhiệm Vụ Thám Hiểm "Hy Vọng Không Băng Giá"</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Hoàn thành Chuyện Sau Cùng "Tất Cả Ánh Nắng Chạm Đến"</t>
+          <t>Hoàn thành Câu Chuyện Sau "Ánh Nắng Chạm Đến Mọi Thứ"</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách đua Route Constructor cụ thể</t>
+          <t>Hoàn thành các thử thách Đua Xây Dựng Đường đặc biệt</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Hoàn thành điều tra các sông băng cụ thể trong "Ice Seal Breaker"</t>
+          <t>Hoàn thành điều tra các sông băng đặc biệt trong "Ice Seal Breaker"</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Điều tra các vật phẩm trong cabin sau khi hoàn thành Nhiệm Vụ Chính "Ngôi Sao Viễn Du"</t>
+          <t>Kiểm tra các vật phẩm trong cabin sau khi hoàn thành Nhiệm Vụ Chính "Ngôi Sao Lang Thang Xa Xôi"</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Projector: Glommoth</t>
+          <t>Máy chiếu: Glommoth</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Thử thách đua Route Constructor</t>
+          <t>Thử Thách Đua Xe Xây Dựng Tuyến Đường</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Ice Seal Breaker</t>
+          <t>Phá Ấn Băng</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Ginnungamere Cabin</t>
+          <t>Lều Ginnungamere</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Dùng Projector: Glommoth để phá vỡ một số khối băng nhất định</t>
+          <t>Dùng Máy Chiếu: Glommoth để đập vỡ các khối băng nhất định</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách đua Route Constructor cụ thể</t>
+          <t>Hoàn thành các thử thách Đua Xây Dựng Đường đặc biệt</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Điều tra vật phẩm trong cabin Ginnungamere</t>
+          <t>Kiểm tra các vật phẩm trong cabin Ginnungamere</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ Thám hiểm "Bài ca Băng và Thép" để mở khóa</t>
+          <t>Hoàn thành Nhiệm Vụ Thám Hiểm "Khúc Ca Đá Và Thép" để mở khóa.</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Revived Greenwood</t>
+          <t>Greenwood đã hồi sinh</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Greenery From Distant Eons</t>
+          <t>Vùng Xanh Từ Kỷ Nguyên Xa Xưa</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>A Warm Haven</t>
+          <t>Nơi Ấm Áp</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>The Fallen Gaze</t>
+          <t>Ánh Nhìn Sa Ngã</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>The Resting Colossus</t>
+          <t>Người Khổng Lồ An Nghỉ</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Yearning For Roaming</t>
+          <t>Khát Khao Lang Thang</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>The Frozen Passage</t>
+          <t>Hành Lang Băng Giá</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Icebound Desire</t>
+          <t>Khát Vọng Băng Giá</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Snowcovered Homeland</t>
+          <t>Quê Hương Phủ Tuyết</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Lời Nguyện Cũ từ Biển Sao</t>
+          <t>Ước Nguyện Xưa Từ Biển Sao</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Những Người Tiên Phong ở Everwinter</t>
+          <t>Những Nhà Tiên Phong tại Everwinter</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Không xác định</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Startorch Academy</t>
+          <t>Học viện Startorch</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Guiding Starlance</t>
+          <t>Ngọn Giáo Dẫn Lối</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Không xác định</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Nam</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>New Federation</t>
+          <t>Liên Bang Mới</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Startorch Academy</t>
+          <t>Học viện Startorch</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Giai Đoạn Chuyển Tiếp</t>
+          <t>Chuyển Tiếp Giai Đoạn</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Game Cartridge</t>
+          <t>Băng Trò Chơi</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Exostrider Figurine</t>
+          <t>Mô hình Exostrider</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Paper Plane</t>
+          <t>Máy Bay Giấy</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Non-Prescription Glasses</t>
+          <t>Kính Mắt Không Đơn</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Medical Gloves</t>
+          <t>Găng Tay Y Tế</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Faded Candy Wrapper Bookmark</t>
+          <t>Dấu trang bằng giấy gói kẹo phai màu</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>The Young Ones</t>
+          <t>Những Đứa Trẻ</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Chỉ Những Gì Vô Hình Mới Nhìn Thấy</t>
+          <t>Chỉ những kẻ vô hình mới được nhìn thấy</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Every Unspoken Word</t>
+          <t>Mỗi Lời Chưa Nói</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>"Brother"</t>
+          <t>"Anh trai"</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Undercurrent</t>
+          <t>Dòng ngầm</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Dark Clouds</t>
+          <t>Mây Đen U Ám</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Storm</t>
+          <t>Bão Tố</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Sau Khi Băng Tan</t>
+          <t>Sau Cơn Tan Băng</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Dùng Aemeath để vượt Tháp Nguy Hiểm Tầng 1 đến Tầng 4 trong Tháp Nghịch Cảnh: Khu Vực Nguy Hiểm</t>
+          <t>Dùng Aemeath để vượt Tháp Hazard từ Tầng 1 đến Tầng 4 trong Tower of Adversity: Hazard Zone</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Dùng Augusta để vượt Tháp Nguy Hiểm Tầng 1 đến Tầng 4 trong Tháp Nghịch Cảnh: Khu Vực Nguy Hiểm</t>
+          <t>Dùng Augusta để vượt từ tầng 1 đến tầng 4 của Hazard Tower trong Tower of Adversity: Hazard Zone</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Dùng Phrolova để vượt Tháp Nguy Hiểm Tầng 1 đến Tầng 4 trong Tháp Nghịch Cảnh: Khu Vực Nguy Hiểm</t>
+          <t>Dùng Phrolova để vượt Tháp Nguy Hiểm từ tầng 1 đến tầng 4 trong Tháp Thử Thách: Vùng Nguy Hiểm.</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Dùng Cartethyia để vượt Tháp Nguy Hiểm Tầng 1 đến Tầng 4 trong Tháp Nghịch Cảnh: Khu Vực Nguy Hiểm</t>
+          <t>Dùng Cartethyia để vượt từ tầng 1 đến tầng 4 của Tháp Nguy Hiểm trong Tower of Adversity: Hazard Zone</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Dùng Carlotta để vượt Tháp Nguy Hiểm Tầng 1 đến Tầng 4 trong Tháp Nghịch Cảnh: Khu Vực Nguy Hiểm</t>
+          <t>Dùng Carlotta để vượt qua từ Tầng 1 đến Tầng 4 của Tháp Hazard trong "Tháp Nghịch Cảnh: Vùng Nguy Hiểm"</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Dùng Aemeath để vượt Vùng Nước Tái Sinh: Dòng Chảy Xiết ở Whimpering Wastes</t>
+          <t>Dùng Aemeath để vượt ải Respawning Waters: Torrents ở Whimpering Wastes</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Dùng Luuk Herssen để vượt Vùng Nước Tái Sinh: Dòng Chảy Xiết ở Whimpering Wastes</t>
+          <t>Dùng Luuk Herssen để vượt qua Dòng Nước Hồi Sinh: Thác Nước ở Vùng Đất Than Thở</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Dùng Augusta hoặc Carlotta để hoàn thành Respawning Waters: Torrents ở Whimpering Wastes</t>
+          <t>Dùng Augusta hoặc Carlotta để vượt ải Respawning Waters: Torrents ở Whimpering Wastes</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Dùng Cartethyia hoặc Zani để hoàn thành Respawning Waters: Torrents ở Whimpering Wastes</t>
+          <t>Dùng Cartethyia hoặc Zani để vượt ải "Nước Tái Sinh: Dòng Chảy" tại Whimpering Wastes</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Dùng Phrolova hoặc Galbrena để hoàn thành Respawning Waters: Torrents ở Whimpering Wastes</t>
+          <t>Dùng Phrolova hoặc Galbrena để dọn sạch Vùng Nước Tái Sinh: Dòng Chảy ở Whimpering Wastes</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Hoàn thành Stability Accords và Singularity Expansion với bất kỳ đội nào ở Doubled Pawns Matrix</t>
+          <t>Hoàn thành Hiệp Ước Ổn Định và Mở Rộng Điểm Kỳ Dị với bất kỳ đội nào trong Ma Trận Tốt Đôi</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Dùng Luuk Herssen để hoàn thành mỗi khu huấn luyện một lần</t>
+          <t>Dùng Luuk Herssen để hoàn thành từng khu huấn luyện trong ba khu một lần</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Tunability</t>
+          <t>Độ Cộng Hưởng</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Tunability: Rondo</t>
+          <t>Khả năng điều chỉnh: Rondo</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Tunability: Downbeat</t>
+          <t>Độ Cộng Hưởng: Âm Trầm</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Tunability: Afterwave</t>
+          <t>Độ Cộng Hưởng: Hậu Sóng</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>War-Scorched Mark</t>
+          <t>Dấu Vết Bị Chiến Tranh Thiêu Đốt</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Ruler's Edge</t>
+          <t>Lưỡi Kiếm Của Chúa Tể</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Bloodstained Roar</t>
+          <t>Tiếng Gầm Đẫm Máu</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Glorious March</t>
+          <t>Hành Quân Vinh Quang</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Boundary of Lunar Phases</t>
+          <t>Giới Hạn Pha Trăng</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Radiance of Fullest Moon</t>
+          <t>Ánh Sáng Trăng Rằm</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Vast Light of Changes</t>
+          <t>Ánh Sáng Thay Đổi Vô Biên</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Clear Heart of Heaven</t>
+          <t>Chinh phục Trái Tim Bầu Trời</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Ethereal Flow to One</t>
+          <t>Dòng Chảy Siêu Nhiên Đến Một</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Abyssal Descent</t>
+          <t>Sa Xuống Vực Sâu</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Journey Together</t>
+          <t>Cùng Nhau Hành Trình</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Blazing Purgatory</t>
+          <t>Luyện Ngục Rực Cháy</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Everburning Flame</t>
+          <t>Ngọn Lửa Cháy Đời</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Cursed Hellfire</t>
+          <t>Hỏa Ngục Bị Nguyền Rủa</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Blade Rinsed, Edge Honed</t>
+          <t>Kiếm Rửa Sạch, Lưỡi Mài bén</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Autumn Waters Severed</t>
+          <t>Dòng Nước Mùa Thu Đứt Đoạn</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Sleeves Stirred, Mist Arising</t>
+          <t>Tà Áo Lay Động, Sương Mù Dâng Trào</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Impending Snow</t>
+          <t>Bão Tuyết Sắp Ðến</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Khoan to Unsheathe</t>
+          <t>Chờ rút vũ khí</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Unraveling Void</t>
+          <t>Giải Thể Hư Không</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Endgame Snip</t>
+          <t>Đoạn Kết Săn</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Infinite Judgment</t>
+          <t>Phán Quyết Vô Biên</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>String Axiom</t>
+          <t>Chân Lý Axiom</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Severance Horizon</t>
+          <t>Chân Trời Đoạn Tuyệt</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Đáp Ứng Kỳ Vọng</t>
+          <t>Để Đáp Ứng Kỳ Vọng</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Ghi Nhớ Lời Dạy</t>
+          <t>Để Ghi Nhớ Những Lời Dạy</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Chạy Vòng Quanh</t>
+          <t>Để Chạy Vòng Quanh</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Đến Kết Cục Tốt Đẹp</t>
+          <t>Hướng tới Kết Cục Tốt Đẹp</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Tunability: Overtone</t>
+          <t>Độ Cộng Hưởng: Âm Cao</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Tutorial Track</t>
+          <t>Lộ Trình Hướng Dẫn</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Tutorial Track</t>
+          <t>Lộ Trình Hướng Dẫn</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>De Anima</t>
+          <t>Về Linh Hồn</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Whispers of Stars</t>
+          <t>Lời thì thầm của những vì sao</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Moments Captured Among the Stars</t>
+          <t>Khoảnh khắc giữa muôn vì sao</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>To Bright Warm Gold</t>
+          <t>Đến Ánh Vàng Ấm Áp</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Dancing Through Fantasies</t>
+          <t>Nhảy Qua Ảo Giác</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>With Glory I Shall Fall</t>
+          <t>Ta Sẽ Ngã Xuống Trong Vinh Quang</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Daisy Crown</t>
+          <t>Vương Miện Cúc Dại</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Till Dawn</t>
+          <t>Cho Đến Bình Minh</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25774,7 +25774,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Radiance Across Sea and Sky</t>
+          <t>Ánh Sáng Trên Biển Trời</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>A Splash of True Colors (Throttle Up!)</t>
+          <t>Bùng Nổ Sắc Màu Thật Sự (Tăng Tốc!)</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>O Sun, Witness My Name</t>
+          <t>Hỡi Mặt Trời, Xin Chứng Kiến Danh Ta</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>The Sound of Lost Joy</t>
+          <t>Âm Thanh Niềm Vui Đã Mất</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Drizzle &amp; Dolce</t>
+          <t>Mưa Phùn &amp; Ngọt Ngào</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Bước Cuối Cùng!</t>
+          <t>Bước Cuối!</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Wuthering Waves Pioneer Podcast / Yushu</t>
+          <t>Podcast Tiên Phong Sóng Gió Mạnh Mẽ / Yushu</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26334,7 +26334,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Wuthering Waves Pioneer Podcast / Yushu</t>
+          <t>Podcast Tiên Phong Sóng Gió Mạnh Mẽ / Yushu</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Wuthering Waves Pioneer Podcast / jixwang / jkinss</t>
+          <t>Podcast Tiên Phong Sóng Gió Mạnh Mẽ / jixwang / jkinss</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Wuthering Waves Pioneer Podcast / Gokou / Tarokiki</t>
+          <t>Podcast Tiên Phong Sóng Gió Mạnh Mẽ / Gokou / Tarokiki</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Wuthering Waves Pioneer Podcast / Yushu / DaHua</t>
+          <t>Podcast Tiên Phong Sóng Gió Mạnh Mẽ / Yushu / DaHua</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Wuthering Waves Pioneer Podcast / Koimoon / Risa Yuzuki</t>
+          <t>Podcast Tiên Phong Sóng Gió Mạnh Mẽ / Koimoon / Risa Yuzuki</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Wuthering Waves Pioneer Podcast / jixwang / VISION SOUND</t>
+          <t>Podcast Tiên Phong Sóng Gió Mạnh Mẽ / jixwang / VISION SOUND</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Wuthering Waves Pioneer Podcast / jixwang / VISION SOUND</t>
+          <t>Podcast Tiên Phong Sóng Gió Mạnh Mẽ / jixwang / VISION SOUND</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Wuthering Waves Pioneer Podcast / Empty old City</t>
+          <t>Podcast Tiên Phong Sóng Gió Mạnh Mẽ / Thành phố cũ hoang tàn</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Wuthering Waves Pioneer Podcast / baitian / Gone Li / VISION SOUND</t>
+          <t>Podcast Tiên Phong Sóng Gió Mạnh Mẽ / baitian / Gone Li / VISION SOUND</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Wuthering Waves Pioneer Podcast / jixwang / VISION SOUND</t>
+          <t>Podcast Tiên Phong Sóng Gió Mạnh Mẽ / jixwang / VISION SOUND</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Wuthering Waves Pioneer Podcast / Minase</t>
+          <t>Podcast Tiên Phong Sóng Gió Mạnh Mẽ / Minase</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Nebulas Walk</t>
+          <t>Dạo Chơi Tinh Vân</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27384,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Planet Tales</t>
+          <t>Chuyện Kể Hành Tinh</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Star Frontier</t>
+          <t>Tiền Tuyến Sao</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Muse Dash</t>
+          <t>Vũ Điệu Cảm Hứng</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Khúc Ca Băng và Thép</t>
+          <t>Khúc Ca Băng Thép</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Hy Vọng Tan Băng</t>
+          <t>Hy Vọng Đã Tan Băng</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Upptopia</t>
+          <t>Upphopia</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Vượt Qua Tảng Băng</t>
+          <t>Vượt Băng Sơn</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Chill-Zone</t>
+          <t>Vùng Thư Giãn</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Màu Đỏ Rực Cháy Trong Ký Ức</t>
+          <t>Lửa Đỏ Trong Ký Ức</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Hướng Về Cực - Trích Đoạn I</t>
+          <t>Đến Cực - Đoạn Trích I</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Hướng Về Cực - Trích Đoạn II</t>
+          <t>Đến Cực - Đoạn Trích II</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Phim Tài Liệu Về Các Nền Văn Minh: Lahai-Roi - Trích Đoạn I</t>
+          <t>Tài liệu văn minh: Lahai-Roi - Trích đoạn I</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Phim Tài Liệu Về Các Nền Văn Minh: Lahai-Roi - Trích Đoạn II</t>
+          <t>Tài liệu văn minh: Lahai-Roi - Trích đoạn II</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Tổng Quan Dự Án Thám Hiểm Trạm Không Gian Frostlands (Trích Đoạn)</t>
+          <t>Tổng quan về Dự án Thám hiểm Trạm Vũ trụ Frostlands (Trích đoạn)</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Tóm Tắt Dự Án Trạm Không Gian SkyArk (Trích Đoạn)</t>
+          <t>Tóm Tắt Dự Án Trạm Không Gian SkyArk (Trích đoạn)</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Bản Ghi Cuộc Trò Chuyện Với Một Solsworn (Trích Đoạn)</t>
+          <t>Bản ghi cuộc trò chuyện với một Solsworn (Trích đoạn)</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Tóm Tắt Cuộc Trò Chuyện Với Một Solsworn</t>
+          <t>Tổng hợp cuộc trò chuyện với một Solsworn</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Tune Break</t>
+          <t>Đột phá Điệu nhạc</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Tune Break</t>
+          <t>Đột phá Điệu nhạc</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Preset: Voyaging Star</t>
+          <t>Bản dựng sẵn: Ngôi sao Lang Thang</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Preset: Crystal Sky</t>
+          <t>Cài Đặt: Bầu Trời Pha Lê</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Soliskin Guide</t>
+          <t>Hướng Dẫn Thu Thập Soliskin</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Khúc Ca Băng và Thép</t>
+          <t>Khúc Ca Băng Thép</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Roya Frostlands Report</t>
+          <t>Báo Cáo Vùng Đất Băng Giá Roya</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Relative Titans</t>
+          <t>Các Titan Tương Đối</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>The Thật sự Treasure</t>
+          <t>Kho Báu Chân Thật</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>1511 Lines</t>
+          <t>1511 dòng</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Muốn Giàu? Hãy Trồng Cây!</t>
+          <t>Muốn Giàu Nhanh? Hãy Trồng Cây!</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Hoàn thành "Tutorial Track" với bất kỳ Rating nào ở độ khó Easy và Thường</t>
+          <t>Hoàn thành "Hướng Dẫn Theo Dõi" với bất kỳ xếp hạng nào ở độ khó Dễ và Bình Thường</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Hoàn thành "De Anima" ở độ khó Thường với Rating cao hơn A</t>
+          <t>Hoàn thành "De Anima" ở chế độ Thường với xếp hạng cao hơn A.</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Hoàn thành "Whispers of Stars" ở độ khó Thường với Rating cao hơn A</t>
+          <t>Hoàn thành "Lời Thì Thầm Của Những Vì Sao" ở độ khó Normal với xếp hạng trên A.</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Hoàn thành "Moments Captured Among the Stars" ở độ khó Thường với Rating cao hơn A</t>
+          <t>Hoàn thành "Khoảnh Khắc Giữa Ngân Hà" ở độ khó Thường với xếp hạng cao hơn A</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Hoàn thành "To Bright Warm Gold" ở độ khó Thường với Rating cao hơn A</t>
+          <t>Hoàn thành "Hướng Tới Ánh Vàng Ấm Áp" ở chế độ Thường với xếp hạng cao hơn A.</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Hoàn thành "Dancing Through Fantasies" ở độ khó Thường với Rating cao hơn A</t>
+          <t>Hoàn thành "Nhảy Múa Giữa Ảo Vọng" ở chế độ Thường với xếp hạng trên A</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Hoàn thành "With Glory I Shall Fall" ở độ khó Thường với Rating cao hơn A</t>
+          <t>Hoàn thành "Vinh Quang Hay Là Cái Chết" ở độ khó Thường với xếp hạng cao hơn A.</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Hoàn thành "Daisy Crown" ở độ khó Thường với Rating cao hơn A</t>
+          <t>Hoàn thành "Vương Miện Cúc" ở chế độ Thường với xếp hạng trên A</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Hoàn thành "Till Dawn" ở độ khó Thường với Rating cao hơn A</t>
+          <t>Hoàn thành "Cho Đến Bình Minh" ở chế độ Thường với xếp hạng cao hơn A.</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Hoàn thành "Radiance Across Sea and Sky" ở độ khó Thường với Rating cao hơn A</t>
+          <t>Hoàn thành "Ánh Sáng Trên Biển Trời" ở mức Độ Khó Thường với Đánh Giá trên A</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Hoàn thành "A Splash of True Colors (Throttle Up!)" ở độ khó Thường với Rating cao hơn A</t>
+          <t>Hoàn thành "Sắc Màu Chân Thật (Tăng Tốc!)" ở mức Độ Khó Bình Thường với Đánh Giá trên A.</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Hoàn thành "O Sun, Witness My Name" ở độ khó Thường với Rating cao hơn A</t>
+          <t>Hoàn thành "Hỡi Mặt Trời, Xin Chứng Kiến Tên Ta" ở độ khó Thường với xếp hạng cao hơn A</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Hoàn thành "The Sound of Lost Joy" ở độ khó Thường với Rating cao hơn A</t>
+          <t>Hoàn thành "Âm Thanh Của Niềm Vui Đã Mất" ở chế độ Thường với xếp hạng cao hơn A.</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30464,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Hoàn thành "Drizzle &amp; Dolce" ở độ khó Thường với Rating cao hơn A</t>
+          <t>Hoàn thành "Mưa Phùn &amp; Ngọt Ngào" ở chế độ Thường với xếp hạng cao hơn A.</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Hoàn thành "Final Step!" ở độ khó Thường với Rating cao hơn A</t>
+          <t>Hoàn thành "Bước Cuối Cùng!" ở chế độ Thường với xếp hạng cao hơn A.</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Hoàn thành "Cthugha" ở độ khó Thường với Rating cao hơn A</t>
+          <t>Hoàn thành "Cthugha" ở chế độ Thường với xếp hạng trên A</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Hoàn thành tổng cộng 6 bản nhạc ở độ khó Thường với Rating cao hơn A</t>
+          <t>Hoàn thành 6 bản nhạc ở chế độ Thường với tổng Đánh Giá trên A</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Hoàn thành tổng cộng 12 bản nhạc ở độ khó Thường với Rating cao hơn A</t>
+          <t>Hoàn thành 12 bản nhạc cấp Độ Thường với tổng Đánh Giá trên A</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Hoàn thành tổng cộng 4 bản nhạc ở độ khó Thường với Rating cao hơn A</t>
+          <t>Hoàn thành tổng cộng 4 bản nhạc ở độ khó Normal với Đánh Giá trên A</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Hoàn thành tổng cộng 8 bản nhạc ở độ khó Thường với Rating cao hơn A</t>
+          <t>Hoàn thành 8 bản nhạc ở chế độ Thường với tổng Đánh Giá trên A</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Hoàn thành tổng cộng 12 bản nhạc ở độ khó Thường với Rating cao hơn A</t>
+          <t>Hoàn thành 12 bản nhạc cấp Độ Thường với tổng Đánh Giá trên A</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Hoàn thành tổng cộng 15 bản nhạc ở độ khó Thường với Rating cao hơn A</t>
+          <t>Hoàn thành 15 bản nhạc ở cấp Normal với tổng đánh giá trên A</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Hoàn thành 1 bản nhạc ở độ khó Khó với Rating cao hơn S</t>
+          <t>Hoàn thành một bản nhạc ở độ khó Hard với Rating cao hơn S</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Hoàn thành 2 bản nhạc ở độ khó Khó với Rating cao hơn S</t>
+          <t>Hoàn thành 2 bản nhạc ở cấp Hard với đánh giá trên S</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Hoàn thành 4 bản nhạc ở độ khó Khó với Rating cao hơn S</t>
+          <t>Hoàn thành 4 bản nhạc ở độ khó Hard với Đánh Giá trên S</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Hoàn thành 6 bản nhạc ở độ khó Khó với Đánh giá cao hơn SS</t>
+          <t>Hoàn thành 6 bản nhạc ở độ khó Hard với Đánh Giá cao hơn SS.</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Đạt Đánh giá cao hơn A ở độ khó Easy trong "Tutorial Track" để mở khóa</t>
+          <t>Đạt Đánh Giá trên A ở độ khó Dễ trong "Hướng Dẫn Cơ Bản" để mở khóa</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Đạt Đánh giá cao hơn A ở độ khó Thường trong "Tutorial Track" để mở khóa</t>
+          <t>Đạt xếp hạng trên A ở độ khó Bình Thường trong "Nhịp Điệu Hướng Dẫn" để mở khóa</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Đạt Đánh giá cao hơn A ở độ khó Easy hoặc Thường trong "De Anima" để mở khóa</t>
+          <t>Đạt Đánh Giá trên A ở độ khó Dễ hoặc Thường trong "De Anima" để mở khóa</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Đạt Đánh giá cao hơn A ở độ khó Easy hoặc Thường trong "Whispers of Stars" để mở khóa</t>
+          <t>Đạt Đánh Giá trên A ở độ khó Dễ hoặc Thường trong "Lời Thì Thầm Của Những Vì Sao" để mở khóa</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Đạt Đánh giá cao hơn A ở độ khó Easy hoặc Thường trong "To Bright Warm Gold" để mở khóa</t>
+          <t>Đạt Đánh Giá trên A ở độ khó Dễ hoặc Thường trong "Hướng Về Ánh Vàng Ấm Áp" để mở khóa</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Đạt Đánh giá cao hơn A ở độ khó Easy hoặc Thường trong "Dancing Through Fantasies" để mở khóa</t>
+          <t>Đạt Đánh Giá trên A ở độ khó Dễ hoặc Thường trong "Nhảy Múa Giữa Ảo Vọng" để mở khóa</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Đạt Đánh giá cao hơn A ở độ khó Easy hoặc Thường trong "With Glory I Shall Fall" để mở khóa</t>
+          <t>Đạt Đánh Giá trên A ở độ khó Dễ hoặc Thường trong "Ta Sẽ Ngã Xuống Trong Vinh Quang" để mở khóa</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Đạt Đánh giá cao hơn A ở độ khó Easy hoặc Thường trong "Daisy Crown" để mở khóa</t>
+          <t>Đạt Đánh Giá trên A ở độ khó Dễ hoặc Thường trong "Vương Miện Cúc" để mở khóa</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Đạt Đánh giá cao hơn A ở độ khó Easy hoặc Thường trong "Till Dawn" để mở khóa</t>
+          <t>Đạt Đánh Giá trên A ở độ khó Dễ hoặc Thường trong "Cho Đến Bình Minh" để mở khóa</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Đạt Đánh giá cao hơn A ở độ khó Easy hoặc Thường trong "Radiance Across Sea and Sky" để mở khóa</t>
+          <t>Đạt Đánh Giá trên A ở độ khó Dễ hoặc Thường trong "Ánh Sáng Vượt Biển Trời" để mở khóa</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Đạt Đánh giá cao hơn A ở độ khó Easy hoặc Thường trong "O Sun, Witness My Name" để mở khóa</t>
+          <t>Đạt Đánh Giá trên A ở độ khó Dễ hoặc Thường trong "Hỡi Mặt Trời, Hãy Chứng Kiến Tên Ta" để mở khóa</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Hoàn thành "Tutorial Track" để mở khóa</t>
+          <t>Hoàn thành "Hướng Dẫn Theo Dõi" để mở khóa</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Mở khóa "Dancing Through Fantasies" để mở khóa</t>
+          <t>Mở khóa "Nhảy Múa Giữa Ảo Vọng" để mở</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Mở khóa "Radiance Across Sea and Sky" để mở khóa</t>
+          <t>Mở khóa "Ánh Sáng Vượt Biển Trời" để mở</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32354,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Đạt Đánh giá cao hơn A ở bất kỳ độ khó nào trong "The Sound of Lost Joy" để mở khóa</t>
+          <t>Đạt xếp hạng trên A ở bất kỳ độ khó nào trong "Âm Thanh Niềm Vui Đã Mất" để mở khóa</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Leisure Tasks</t>
+          <t>Nhiệm Vụ Nhàn Hạ</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Nhiệm vụ thử thách</t>
+          <t>Nhiệm Vụ Thử Thách</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ Chính "Gold Suspended in Shadows" để có trải nghiệm tốt hơn</t>
+          <t>Hoàn thành Nhiệm vụ Chính "Vàng Pha Bóng Tối" để có trải nghiệm tốt hơn</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Mornye</t>
+          <t>Chàooo</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Beep Bop</t>
+          <t>Bíp Bóp</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -33054,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Không xác định</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Roya Tribe</t>
+          <t>Bộ Lạc Roya</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>True Name Manifestation</t>
+          <t>Chân Danh Thể Hiện</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Dấu hiệu của Sự sống</t>
+          <t>Dấu Vết Sự Sống</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Người mang Niềm đam mê</t>
+          <t>Người Mang Theo Đam Mê</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>A Mother's Love</t>
+          <t>Tình Mẫu Tử</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Her Family</t>
+          <t>Gia Đình Cô Ấy</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Her Gift</t>
+          <t>Tài Năng Của Nàng</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Her Limits</t>
+          <t>Giới Hạn Của Nàng</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Her Shadow</t>
+          <t>Bóng Dáng Của Nàng</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Her Words</t>
+          <t>Lời của cô ấy</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
